--- a/experiment/SRForm2_bestx4/Test/results_table.xlsx
+++ b/experiment/SRForm2_bestx4/Test/results_table.xlsx
@@ -570,38 +570,38 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>31.796/
-0.8877</t>
+          <t>31.895/
+0.8894</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>28.344/
-0.7751</t>
+          <t>28.389/
+0.7767</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>27.402/
-0.7307</t>
+          <t>27.433/
+0.7324</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>25.545/
-0.7680</t>
+          <t>25.658/
+0.7726</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>29.640/
-0.8976</t>
+          <t>29.826/
+0.9000</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>28.545/
-0.8118</t>
+          <t>28.640/
+0.8142</t>
         </is>
       </c>
     </row>
